--- a/out/MLP-mamba2_repeat_3_000001.xlsx
+++ b/out/MLP-mamba2_repeat_3_000001.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.901262215535431</v>
+        <v>1.633306561630227</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.50126221553543</v>
+        <v>1.633306561630227</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5903981995424215</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.901262215535431</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.901262215535431</v>
+        <v>1.633306561630227</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542422</v>
+        <v>1.633306561630227</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.50126221553543</v>
+        <v>1.633306561630227</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.000304291524944827</v>
+        <v>-0.0002824062474943931</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1310190958677621</v>
+        <v>0.1215958237375037</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2623878470620755</v>
+        <v>0.2435163695505434</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5061960572132793</v>
+        <v>0.4697898008232049</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.14409591499324</v>
+        <v>1.061810885509346</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1557087447879883</v>
+        <v>0.1445094672276252</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.948676545863206</v>
+        <v>0.8804463240589255</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03159446258013456</v>
+        <v>0.02932225242020544</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8559131347640406</v>
+        <v>0.794354270785031</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02736220874353217</v>
+        <v>0.02539437376145378</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.879008161567597</v>
+        <v>0.8157883497432559</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01337676285983281</v>
+        <v>0.01241473299779661</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8783641837675087</v>
+        <v>0.8151906855304432</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006382052430573726</v>
+        <v>0.00592301853374308</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8777362006540892</v>
+        <v>0.8146075054588818</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002656074770534405</v>
+        <v>0.002464566460688415</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.901262215535431</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8766582959353302</v>
+        <v>0.8136068139667448</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001839294861162432</v>
+        <v>0.001706567364877938</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8776784014187397</v>
+        <v>0.8145531461685029</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007649229932789252</v>
+        <v>0.0007095143092437892</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8773669476714826</v>
+        <v>0.8142637468331824</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003938984518309985</v>
+        <v>0.0003651670725533889</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8773896880519276</v>
+        <v>0.8142844908851721</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001519343618486195</v>
+        <v>0.0001403873519467144</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.877298519974906</v>
+        <v>0.8141995194545185</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.032235593904744e-05</v>
+        <v>7.459602332568856e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8773076285729308</v>
+        <v>0.8142076365500398</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.735037991412098e-05</v>
+        <v>3.39623495209913e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8773013372106713</v>
+        <v>0.8142014405256663</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.471454777712014e-05</v>
+        <v>1.364889654592446e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8772939000869412</v>
+        <v>0.8141941652992521</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.762265212117796e-06</v>
+        <v>2.839921505579082e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8772861520917518</v>
+        <v>0.8141866348268642</v>
       </c>
     </row>
     <row r="60">
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.877280233538881</v>
+        <v>0.81418076410056</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8772742721102964</v>
+        <v>0.8141748993045588</v>
       </c>
     </row>
     <row r="62">
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8772685929335882</v>
+        <v>0.8141692201278505</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8772637116353389</v>
+        <v>0.8141643388296012</v>
       </c>
     </row>
     <row r="64">
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.877258790433791</v>
+        <v>0.8141594176280533</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8772587824626965</v>
+        <v>0.8141594096569589</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8772589418845856</v>
+        <v>0.814159569078848</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.8141594734257145</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8772591969596085</v>
+        <v>0.8141598241538708</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8772589498556801</v>
+        <v>0.8141595770499425</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8772589100002078</v>
+        <v>0.8141595371944702</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.8141594734257145</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.8141595451655647</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.8141594734257145</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8772589498556801</v>
+        <v>0.8141595770499425</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8772590455088138</v>
+        <v>0.8141596727030762</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8772589817400579</v>
+        <v>0.8141596089343203</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8772589418845856</v>
+        <v>0.814159569078848</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.8141595451655647</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8772586708673742</v>
+        <v>0.8141592980616366</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8772585911564293</v>
+        <v>0.8141592183506917</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8772586389829962</v>
+        <v>0.8141592661772584</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8772587585494132</v>
+        <v>0.8141593857436755</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5903981995424215</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8772587426072243</v>
+        <v>0.8141593698014866</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8772587585494132</v>
+        <v>0.8141593857436755</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8772587426072243</v>
+        <v>0.8141593698014866</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.8141594255991478</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.8141594255991478</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.50126221553543</v>
+        <v>1.633306561630227</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.8141594255991478</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8772589498556801</v>
+        <v>0.8141595770499425</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8772591650752306</v>
+        <v>0.814159792269493</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8772590773931916</v>
+        <v>0.814159704587454</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.50126221553543</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8772590295666249</v>
+        <v>0.8141596567608872</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8772590773931916</v>
+        <v>0.814159704587454</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8772588940580189</v>
+        <v>0.8141595212522813</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8772589020291134</v>
+        <v>0.8141595292233758</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.901262215535431</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8772589100002078</v>
+        <v>0.8141595371944702</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.8141595451655647</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.8141595451655647</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.901262215535431</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8772589578267745</v>
+        <v>0.8141595850210369</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8772590215955305</v>
+        <v>0.8141596487897927</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8772591331908528</v>
+        <v>0.8141597603851152</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8772591810174195</v>
+        <v>0.8141598082116819</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8772591411619473</v>
+        <v>0.8141597683562096</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.901262215535431</v>
+        <v>1.633306561630227</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8772590694220972</v>
+        <v>0.8141596966163596</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.877259188988514</v>
+        <v>0.8141598161827763</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8772590295666249</v>
+        <v>0.8141596567608872</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.8141594255991478</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8772587505783187</v>
+        <v>0.8141593777725811</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8772587824626965</v>
+        <v>0.8141594096569589</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.8141594734257145</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.8141594734257145</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8772587665205076</v>
+        <v>0.81415939371477</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8772586469540906</v>
+        <v>0.8141592741483529</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8772586070986182</v>
+        <v>0.8141592342928806</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8772587505783187</v>
+        <v>0.8141593777725811</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8772588860869245</v>
+        <v>0.8141595132811869</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8772588701447356</v>
+        <v>0.814159497338998</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.8141594734257145</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8772588063759799</v>
+        <v>0.8141594335702422</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>-1.313807099391461</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.877258702751752</v>
+        <v>0.8141593299460144</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8772585831853349</v>
+        <v>0.8141592103795973</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.877258702751752</v>
+        <v>0.8141593299460144</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.50126221553543</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8772587505783187</v>
+        <v>0.8141593777725811</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.8141594734257145</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.7138070993914605</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8772587266650353</v>
+        <v>0.8141593538592977</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>2.233306561630227</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8772587346361298</v>
+        <v>0.8141593618303922</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000001.xlsx
+++ b/out/MLP-mamba2_repeat_3_000001.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.4094390911976031</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA3" t="n">
         <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>0</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>0</v>
       </c>
       <c r="JB7" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA10" t="n">
         <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>2.50126221553543</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9682,14 +9682,14 @@
       </c>
       <c r="IZ11" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA11" t="n">
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11272,14 +11272,14 @@
       </c>
       <c r="IZ13" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA13" t="n">
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>1</v>
       </c>
       <c r="JB15" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>1</v>
       </c>
       <c r="JB16" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>1</v>
       </c>
       <c r="JB17" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16837,14 +16837,14 @@
       </c>
       <c r="IZ20" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA20" t="n">
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23204,7 +23204,7 @@
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>0</v>
       </c>
       <c r="JB35" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>1</v>
       </c>
       <c r="JB39" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,10 +35129,10 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.000304291524944827</v>
+        <v>-0.0002363517952229595</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1310190958677621</v>
+        <v>0.1017661137303329</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2623878470620755</v>
+        <v>0.2038040292829969</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.5061960572132793</v>
+        <v>0.3931763166813904</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>1</v>
       </c>
       <c r="JB45" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636436</v>
       </c>
       <c r="JC45" t="n">
-        <v>1.14409591499324</v>
+        <v>0.8886522336910746</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1557087447879883</v>
+        <v>0.1209432390442922</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.948676545863206</v>
+        <v>0.7368640293722458</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.03159446258013456</v>
+        <v>0.02454028285635458</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38309,10 +38309,10 @@
         <v>0</v>
       </c>
       <c r="JB47" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.8559131347640406</v>
+        <v>0.6648115460819921</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02736220874353217</v>
+        <v>0.02125333338280373</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39104,10 +39104,10 @@
         <v>0</v>
       </c>
       <c r="JB48" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.879008161567597</v>
+        <v>0.6827503867926052</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01337676285983281</v>
+        <v>0.01038992250999097</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.8783641837675087</v>
+        <v>0.6822501841078406</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.006382052430573726</v>
+        <v>0.004956174212470962</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>0</v>
       </c>
       <c r="JB50" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.8777362006540892</v>
+        <v>0.6817612718096498</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.002656074770534405</v>
+        <v>0.00206206498389001</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.8766582959353302</v>
+        <v>0.6809228627676517</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001839294861162432</v>
+        <v>0.001427222285488482</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.8776784014187397</v>
+        <v>0.6817141431659499</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0007649229932789252</v>
+        <v>0.0005928983579605377</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.8773669476714826</v>
+        <v>0.6814710331368449</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003938984518309985</v>
+        <v>0.0003050316275537409</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>0</v>
       </c>
       <c r="JB54" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.8773896880519276</v>
+        <v>0.6814875988269506</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001519343618486195</v>
+        <v>0.0001167684680564539</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>0</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.877298519974906</v>
+        <v>0.6814155958359825</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>8.032235593904744e-05</v>
+        <v>6.14254583149631e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.8773076285729308</v>
+        <v>0.6814215903034159</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>3.735037991412098e-05</v>
+        <v>2.775096046692022e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>0</v>
       </c>
       <c r="JB57" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.8773013372106713</v>
+        <v>0.6814155836788407</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.471454777712014e-05</v>
+        <v>1.045194285233741e-05</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>0</v>
       </c>
       <c r="JB58" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.8772939000869412</v>
+        <v>0.6814086666068626</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>3.762265212117796e-06</v>
+        <v>1.917577799040367e-06</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>0</v>
       </c>
       <c r="JB59" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.8772861520917518</v>
+        <v>0.6814014971369761</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-1.279375894546688e-06</v>
+        <v>-2.106181251314092e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>0</v>
       </c>
       <c r="JB60" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.877280233538881</v>
+        <v>0.6813957720788396</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.410678356938051e-06</v>
+        <v>-3.728542685550439e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.8772742721102964</v>
+        <v>0.6813900029359721</v>
       </c>
     </row>
     <row r="62">
@@ -50234,10 +50234,10 @@
         <v>0</v>
       </c>
       <c r="JB62" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.8772685929335882</v>
+        <v>0.6813844592678696</v>
       </c>
     </row>
     <row r="63">
@@ -51029,10 +51029,10 @@
         <v>1</v>
       </c>
       <c r="JB63" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.8772637116353389</v>
+        <v>0.6813795381141482</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>-4.737866375420875e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.877258790433791</v>
+        <v>0.6813795779696205</v>
       </c>
     </row>
     <row r="65">
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.8772587824626965</v>
+        <v>0.681379569998526</v>
       </c>
     </row>
     <row r="66">
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.8772589418845856</v>
+        <v>0.6813797294204151</v>
       </c>
     </row>
     <row r="67">
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.6813796337672816</v>
       </c>
     </row>
     <row r="68">
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.8772591969596085</v>
+        <v>0.6813799844954379</v>
       </c>
     </row>
     <row r="69">
@@ -55799,10 +55799,10 @@
         <v>0</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.8772589498556801</v>
+        <v>0.6813797373915096</v>
       </c>
     </row>
     <row r="70">
@@ -56594,10 +56594,10 @@
         <v>0</v>
       </c>
       <c r="JB70" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.8772589100002078</v>
+        <v>0.6813796975360373</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.6813796337672816</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.6813797055071318</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.6813796337672816</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>1</v>
       </c>
       <c r="JB74" t="n">
-        <v>2.50126221553543</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.8772589498556801</v>
+        <v>0.6813797373915096</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.8772590455088138</v>
+        <v>0.6813798330446433</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.8772589817400579</v>
+        <v>0.6813797692758874</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.8772589418845856</v>
+        <v>0.6813797294204151</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.6813797055071318</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.8772586708673742</v>
+        <v>0.6813794584032037</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>0</v>
       </c>
       <c r="JB80" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.8772585911564293</v>
+        <v>0.6813793786922588</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>1</v>
       </c>
       <c r="JB81" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.8772586389829962</v>
+        <v>0.6813794265188255</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>0</v>
       </c>
       <c r="JB82" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.8772587585494132</v>
+        <v>0.6813795460852426</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.8772587426072243</v>
+        <v>0.6813795301430537</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>0</v>
       </c>
       <c r="JB84" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.8772587585494132</v>
+        <v>0.6813795460852426</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>1</v>
       </c>
       <c r="JB85" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.8772587426072243</v>
+        <v>0.6813795301430537</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.6813795859407149</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.6813795859407149</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.6813795859407149</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.8772589498556801</v>
+        <v>0.6813797373915096</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>1</v>
       </c>
       <c r="JB90" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.8772591650752306</v>
+        <v>0.6813799526110601</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.8772590773931916</v>
+        <v>0.6813798649290211</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.8772590295666249</v>
+        <v>0.6813798171024543</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.8772590773931916</v>
+        <v>0.6813798649290211</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.8772588940580189</v>
+        <v>0.6813796815938484</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.8772589020291134</v>
+        <v>0.6813796895649429</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.8772589100002078</v>
+        <v>0.6813796975360373</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>0</v>
       </c>
       <c r="JB97" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.6813797055071318</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.8772589179713023</v>
+        <v>0.6813797055071318</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>1</v>
       </c>
       <c r="JB99" t="n">
-        <v>1.901262215535431</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.8772589578267745</v>
+        <v>0.681379745362604</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>1</v>
       </c>
       <c r="JB100" t="n">
-        <v>2.50126221553543</v>
+        <v>1.669436947795724</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.8772590215955305</v>
+        <v>0.6813798091313599</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>1</v>
       </c>
       <c r="JB101" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.8772591331908528</v>
+        <v>0.6813799207266823</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.8772591810174195</v>
+        <v>0.681379968553249</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>0</v>
       </c>
       <c r="JB103" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.8772591411619473</v>
+        <v>0.6813799286977767</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>1</v>
       </c>
       <c r="JB104" t="n">
-        <v>1.901262215535431</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.8772590694220972</v>
+        <v>0.6813798569579267</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.877259188988514</v>
+        <v>0.6813799765243435</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.8772590295666249</v>
+        <v>0.6813798171024543</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.8772587984048854</v>
+        <v>0.6813795859407149</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.8772587505783187</v>
+        <v>0.6813795381141482</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.8772587824626965</v>
+        <v>0.681379569998526</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.6813796337672816</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.6813796337672816</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.8772587665205076</v>
+        <v>0.6813795540563371</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.8772586469540906</v>
+        <v>0.68137943448992</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.8772586070986182</v>
+        <v>0.6813793946344477</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>1</v>
       </c>
       <c r="JB115" t="n">
-        <v>2.50126221553543</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.8772587505783187</v>
+        <v>0.6813795381141482</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.8772588860869245</v>
+        <v>0.681379673622754</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.4505587654005176</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.8772588701447356</v>
+        <v>0.6813796576805651</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>0</v>
       </c>
       <c r="JB118" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.6813796337672816</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>0</v>
       </c>
       <c r="JB119" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.8772588063759799</v>
+        <v>0.6813795939118094</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-1.190398199542422</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.877258702751752</v>
+        <v>0.6813794902875815</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>1</v>
       </c>
       <c r="JB121" t="n">
-        <v>2.50126221553543</v>
+        <v>0.05610647233156292</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.8772585831853349</v>
+        <v>0.6813793707211644</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.9627717100636434</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.877258702751752</v>
+        <v>0.6813794902875815</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>1</v>
       </c>
       <c r="JB123" t="n">
-        <v>2.50126221553543</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.8772587505783187</v>
+        <v>0.6813795381141482</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.5903981995424215</v>
+        <v>0.256106472331563</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.8772588462314522</v>
+        <v>0.6813796337672816</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.5903981995424215</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.8772587266650353</v>
+        <v>0.6813795142008648</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>0</v>
       </c>
       <c r="JB126" t="n">
-        <v>-1.190398199542422</v>
+        <v>-0.6505587654005177</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.8772587346361298</v>
+        <v>0.6813795221719593</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000001.xlsx
+++ b/out/MLP-mamba2_repeat_3_000001.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.2870924472808838</v>
       </c>
       <c r="JB2" t="n">
-        <v>0.4094390911976031</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>1</v>
+        <v>0.7095795869827271</v>
       </c>
       <c r="JB3" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.58</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.3475010097026825</v>
       </c>
       <c r="JB4" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4916,10 +4916,10 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0</v>
+        <v>0.1942663043737411</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.2582058310508728</v>
       </c>
       <c r="JB6" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0</v>
+        <v>0.2544656693935394</v>
       </c>
       <c r="JB7" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7301,10 +7301,10 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.3303287625312805</v>
       </c>
       <c r="JB8" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.3631916344165802</v>
       </c>
       <c r="JB9" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>1</v>
+        <v>0.5085197687149048</v>
       </c>
       <c r="JB10" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.3054375052452087</v>
       </c>
       <c r="JB11" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.2525750398635864</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.3143773972988129</v>
       </c>
       <c r="JB13" t="n">
-        <v>0.256106472331563</v>
+        <v>0.16</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5351336598396301</v>
       </c>
       <c r="JB14" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12866,10 +12866,10 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>1</v>
+        <v>0.576799750328064</v>
       </c>
       <c r="JB15" t="n">
-        <v>1.669436947795724</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>1</v>
+        <v>0.7204849720001221</v>
       </c>
       <c r="JB16" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>1</v>
+        <v>0.5754132270812988</v>
       </c>
       <c r="JB17" t="n">
-        <v>0.9627717100636436</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15251,10 +15251,10 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.4252062439918518</v>
       </c>
       <c r="JB18" t="n">
-        <v>0.256106472331563</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4794808626174927</v>
       </c>
       <c r="JB19" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.547101616859436</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.3556079566478729</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.2640213370323181</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.2505334615707397</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.1727255582809448</v>
       </c>
       <c r="JB24" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20816,10 +20816,10 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.51835697889328</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3558023869991302</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>0</v>
+        <v>0.3297553658485413</v>
       </c>
       <c r="JB27" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.3072896599769592</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.3962659239768982</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.4285559952259064</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.2365186512470245</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26377,14 +26377,14 @@
       </c>
       <c r="IZ32" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.4184211790561676</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27172,14 +27172,14 @@
       </c>
       <c r="IZ33" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.1322172731161118</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4796909987926483</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0</v>
+        <v>0.3126256465911865</v>
       </c>
       <c r="JB35" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.3</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4269334971904755</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30356,10 +30356,10 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.3863523006439209</v>
       </c>
       <c r="JB37" t="n">
-        <v>0.256106472331563</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31151,10 +31151,10 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>1</v>
+        <v>0.5070080757141113</v>
       </c>
       <c r="JB38" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>1</v>
+        <v>0.6210157871246338</v>
       </c>
       <c r="JB39" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>1</v>
+        <v>0.8631818294525146</v>
       </c>
       <c r="JB40" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33536,10 +33536,10 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>1</v>
+        <v>0.7516226768493652</v>
       </c>
       <c r="JB41" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.9642179012298584</v>
       </c>
       <c r="JB42" t="n">
-        <v>1.669436947795724</v>
+        <v>0.9999999999999998</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,13 +35126,13 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.8121073246002197</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.669436947795724</v>
+        <v>0.8599999999999999</v>
       </c>
       <c r="JC43" t="n">
-        <v>-0.0002363517952229595</v>
+        <v>-0.0001702408744366839</v>
       </c>
     </row>
     <row r="44">
@@ -35913,7 +35913,7 @@
         <v>0</v>
       </c>
       <c r="IY44" t="n">
-        <v>0.1017661137303329</v>
+        <v>0.07330077777373428</v>
       </c>
       <c r="IZ44" t="inlineStr">
         <is>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.9375625252723694</v>
       </c>
       <c r="JB44" t="n">
-        <v>1.669436947795724</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC44" t="n">
-        <v>0.2038040292829969</v>
+        <v>0.1467971759432526</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.3931763166813904</v>
+        <v>0.2831996698953014</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>1</v>
+        <v>0.6953548789024353</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.9627717100636436</v>
+        <v>-0.3</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.8886522336910746</v>
+        <v>0.6400831868157596</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>0.1209432390442922</v>
+        <v>0.08711329698371349</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.01094582583755255</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.7368640293722458</v>
+        <v>0.5307526231656382</v>
       </c>
     </row>
     <row r="47">
@@ -38298,7 +38298,7 @@
         <v>0</v>
       </c>
       <c r="IY47" t="n">
-        <v>0.02454028285635458</v>
+        <v>0.01767614252776867</v>
       </c>
       <c r="IZ47" t="inlineStr">
         <is>
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0</v>
+        <v>0.2179289013147354</v>
       </c>
       <c r="JB47" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.6648115460819921</v>
+        <v>0.4788543111816319</v>
       </c>
     </row>
     <row r="48">
@@ -39093,7 +39093,7 @@
         <v>0</v>
       </c>
       <c r="IY48" t="n">
-        <v>0.02125333338280373</v>
+        <v>0.01530832500785563</v>
       </c>
       <c r="IZ48" t="inlineStr">
         <is>
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0</v>
+        <v>0.01709781400859356</v>
       </c>
       <c r="JB48" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.6827503867926052</v>
+        <v>0.4917752774562403</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.01038992250999097</v>
+        <v>0.00748238961545394</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.494206041097641</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC49" t="n">
-        <v>0.6822501841078406</v>
+        <v>0.4914138391048955</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.004956174212470962</v>
+        <v>0.003568381776201306</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0</v>
+        <v>0.1966165900230408</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC50" t="n">
-        <v>0.6817612718096498</v>
+        <v>0.4910602829844139</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.00206206498389001</v>
+        <v>0.001483643082930753</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5493714809417725</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.3</v>
       </c>
       <c r="JC51" t="n">
-        <v>0.6809228627676517</v>
+        <v>0.4904549732263382</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.001427222285488482</v>
+        <v>0.001026724782164925</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.1937374174594879</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>0.6817141431659499</v>
+        <v>0.4910236470363983</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0005928983579605377</v>
+        <v>0.0004260280188314653</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.6452180743217468</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.256106472331563</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC53" t="n">
-        <v>0.6814710331368449</v>
+        <v>0.4908470842272644</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.0003050316275537409</v>
+        <v>0.0002181693181098049</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0</v>
+        <v>0.2652173340320587</v>
       </c>
       <c r="JB54" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>0.6814875988269506</v>
+        <v>0.4908576145057606</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.0001167684680564539</v>
+        <v>8.265230243718883e-05</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0</v>
+        <v>0.1778687536716461</v>
       </c>
       <c r="JB55" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>0.6814155958359825</v>
+        <v>0.4908043437054495</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>6.14254583149631e-05</v>
+        <v>4.310119395221467e-05</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.3423936069011688</v>
       </c>
       <c r="JB56" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>0.6814215903034159</v>
+        <v>0.4908072705833183</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>2.775096046692022e-05</v>
+        <v>1.871621275190775e-05</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0</v>
+        <v>0.1975788176059723</v>
       </c>
       <c r="JB57" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>0.6814155836788407</v>
+        <v>0.4908015474204531</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>1.045194285233741e-05</v>
+        <v>6.189337927554673e-06</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0</v>
+        <v>0.3115136027336121</v>
       </c>
       <c r="JB58" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>0.6814086666068626</v>
+        <v>0.4907951822846045</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>1.917577799040367e-06</v>
+        <v>-3.882814673064221e-07</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0</v>
+        <v>0.2721310257911682</v>
       </c>
       <c r="JB59" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>0.6814014971369761</v>
+        <v>0.4907886642314969</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>-2.106181251314092e-06</v>
+        <v>-2.932986608081494e-06</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0</v>
+        <v>0.2568386495113373</v>
       </c>
       <c r="JB60" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC60" t="n">
-        <v>0.6813957720788396</v>
+        <v>0.4907831326680945</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>-3.728542685550439e-06</v>
+        <v>-4.04640701416283e-06</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.147075429558754</v>
       </c>
       <c r="JB61" t="n">
-        <v>-0.6505587654005177</v>
+        <v>0.16</v>
       </c>
       <c r="JC61" t="n">
-        <v>0.6813900029359721</v>
+        <v>0.4907775558109437</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>-4.634963333793937e-06</v>
+        <v>-4.817481666896968e-06</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0</v>
+        <v>0.4459397196769714</v>
       </c>
       <c r="JB62" t="n">
-        <v>0.256106472331563</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC62" t="n">
-        <v>0.6813844592678696</v>
+        <v>0.4907721484682867</v>
       </c>
     </row>
     <row r="63">
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>1</v>
+        <v>0.5478038191795349</v>
       </c>
       <c r="JB63" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC63" t="n">
-        <v>0.6813795381141482</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="64">
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.3451752662658691</v>
       </c>
       <c r="JB64" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC64" t="n">
-        <v>0.6813795779696205</v>
+        <v>0.4907672671700376</v>
       </c>
     </row>
     <row r="65">
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.7665900588035583</v>
       </c>
       <c r="JB65" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC65" t="n">
-        <v>0.681379569998526</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="66">
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.2365031540393829</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.16</v>
       </c>
       <c r="JC66" t="n">
-        <v>0.6813797294204151</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="67">
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8914751410484314</v>
       </c>
       <c r="JB67" t="n">
-        <v>0.256106472331563</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC67" t="n">
-        <v>0.6813796337672816</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="68">
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.16587233543396</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC68" t="n">
-        <v>0.6813799844954379</v>
+        <v>0.4907676736958551</v>
       </c>
     </row>
     <row r="69">
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0</v>
+        <v>0.1619214713573456</v>
       </c>
       <c r="JB69" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>0.6813797373915096</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="70">
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0</v>
+        <v>0.3377712368965149</v>
       </c>
       <c r="JB70" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC70" t="n">
-        <v>0.6813796975360373</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.4509402215480804</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC71" t="n">
-        <v>0.6813796337672816</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.2788635492324829</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>0.6813797055071318</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0</v>
+        <v>0.2556007206439972</v>
       </c>
       <c r="JB73" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC73" t="n">
-        <v>0.6813796337672816</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>1</v>
+        <v>0.9558586478233337</v>
       </c>
       <c r="JB74" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC74" t="n">
-        <v>0.6813797373915096</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.1745253354310989</v>
       </c>
       <c r="JB75" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>0.6813798330446433</v>
+        <v>0.4907675222450604</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.1508907824754715</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.4505587654005176</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>0.6813797692758874</v>
+        <v>0.4907674584763045</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0</v>
+        <v>0.224904477596283</v>
       </c>
       <c r="JB77" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC77" t="n">
-        <v>0.6813797294204151</v>
+        <v>0.4907674186208323</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0</v>
+        <v>0.09800317138433456</v>
       </c>
       <c r="JB78" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC78" t="n">
-        <v>0.6813797055071318</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.2036522924900055</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC79" t="n">
-        <v>0.6813794584032037</v>
+        <v>0.4907671476036208</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0</v>
+        <v>0.4688417613506317</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC80" t="n">
-        <v>0.6813793786922588</v>
+        <v>0.490767067892676</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>1</v>
+        <v>0.5553006529808044</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>0.6813794265188255</v>
+        <v>0.4907671157192427</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0</v>
+        <v>0.2687999606132507</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.256106472331563</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>0.6813795460852426</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0</v>
+        <v>0.4707186818122864</v>
       </c>
       <c r="JB83" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>0.6813795301430537</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0</v>
+        <v>0.3846917748451233</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>0.6813795460852426</v>
+        <v>0.4907672352856598</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>1</v>
+        <v>0.5789629220962524</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC85" t="n">
-        <v>0.6813795301430537</v>
+        <v>0.4907672193434709</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.3535565733909607</v>
       </c>
       <c r="JB86" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>0.6813795859407149</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0</v>
+        <v>0.3039943277835846</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.256106472331563</v>
+        <v>0.3</v>
       </c>
       <c r="JC87" t="n">
-        <v>0.6813795859407149</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.8388734459877014</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.3</v>
       </c>
       <c r="JC88" t="n">
-        <v>0.6813795859407149</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3901277780532837</v>
       </c>
       <c r="JB89" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>0.6813797373915096</v>
+        <v>0.4907674265919267</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>1</v>
+        <v>0.7327395081520081</v>
       </c>
       <c r="JB90" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>0.6813799526110601</v>
+        <v>0.4907676418114773</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0</v>
+        <v>0.2327285706996918</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>0.6813798649290211</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5457927584648132</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC92" t="n">
-        <v>0.6813798171024543</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.09769754856824875</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC93" t="n">
-        <v>0.6813798649290211</v>
+        <v>0.4907675541294382</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3698757886886597</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC94" t="n">
-        <v>0.6813796815938484</v>
+        <v>0.4907673707942655</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3053628504276276</v>
       </c>
       <c r="JB95" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>0.6813796895649429</v>
+        <v>0.49076737876536</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6117194294929504</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>0.6813796975360373</v>
+        <v>0.4907673867364544</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0</v>
+        <v>0.2792908847332001</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC97" t="n">
-        <v>0.6813797055071318</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4177703559398651</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.05610647233156292</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>0.6813797055071318</v>
+        <v>0.4907673947075489</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>1</v>
+        <v>0.7329034805297852</v>
       </c>
       <c r="JB99" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC99" t="n">
-        <v>0.681379745362604</v>
+        <v>0.4907674345630212</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>1</v>
+        <v>0.6029258966445923</v>
       </c>
       <c r="JB100" t="n">
-        <v>1.669436947795724</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>0.6813798091313599</v>
+        <v>0.4907674983317771</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>1</v>
+        <v>0.5134434700012207</v>
       </c>
       <c r="JB101" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.3</v>
       </c>
       <c r="JC101" t="n">
-        <v>0.6813799207266823</v>
+        <v>0.4907676099270994</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.2455270439386368</v>
       </c>
       <c r="JB102" t="n">
-        <v>0.256106472331563</v>
+        <v>0.16</v>
       </c>
       <c r="JC102" t="n">
-        <v>0.681379968553249</v>
+        <v>0.4907676577536662</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0</v>
+        <v>0.3067110776901245</v>
       </c>
       <c r="JB103" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>0.6813799286977767</v>
+        <v>0.4907676178981939</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>1</v>
+        <v>0.6113965511322021</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>0.6813798569579267</v>
+        <v>0.4907675461583438</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.1302557438611984</v>
       </c>
       <c r="JB105" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>0.6813799765243435</v>
+        <v>0.4907676657247606</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.1368108242750168</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC106" t="n">
-        <v>0.6813798171024543</v>
+        <v>0.4907675063028715</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2335508614778519</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC107" t="n">
-        <v>0.6813795859407149</v>
+        <v>0.4907672751411321</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.3958383500576019</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>0.6813795381141482</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4419620335102081</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>0.681379569998526</v>
+        <v>0.4907672591989432</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.3863091766834259</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>0.6813796337672816</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.1953750997781754</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>0.6813796337672816</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2087164670228958</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC112" t="n">
-        <v>0.6813795540563371</v>
+        <v>0.4907672432567542</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.2294738590717316</v>
       </c>
       <c r="JB113" t="n">
-        <v>0.256106472331563</v>
+        <v>0.16</v>
       </c>
       <c r="JC113" t="n">
-        <v>0.68137943448992</v>
+        <v>0.4907671236903371</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>1</v>
+        <v>0.6601393222808838</v>
       </c>
       <c r="JB114" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC114" t="n">
-        <v>0.6813793946344477</v>
+        <v>0.4907670838348649</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>1</v>
+        <v>0.5906870365142822</v>
       </c>
       <c r="JB115" t="n">
-        <v>0.9627717100636434</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC115" t="n">
-        <v>0.6813795381141482</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4911705851554871</v>
       </c>
       <c r="JB116" t="n">
-        <v>0.256106472331563</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>0.681379673622754</v>
+        <v>0.4907673628231711</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.1846119314432144</v>
       </c>
       <c r="JB117" t="n">
-        <v>-0.4505587654005176</v>
+        <v>0.16</v>
       </c>
       <c r="JC117" t="n">
-        <v>0.6813796576805651</v>
+        <v>0.4907673468809822</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0</v>
+        <v>0.3049150705337524</v>
       </c>
       <c r="JB118" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>0.6813796337672816</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0</v>
+        <v>0.2293042540550232</v>
       </c>
       <c r="JB119" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC119" t="n">
-        <v>0.6813795939118094</v>
+        <v>0.4907672831122265</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.1202573180198669</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>0.6813794902875815</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>1</v>
+        <v>0.785956859588623</v>
       </c>
       <c r="JB121" t="n">
-        <v>0.05610647233156292</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC121" t="n">
-        <v>0.6813793707211644</v>
+        <v>0.4907670599215815</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.3485607504844666</v>
       </c>
       <c r="JB122" t="n">
-        <v>0.9627717100636434</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC122" t="n">
-        <v>0.6813794902875815</v>
+        <v>0.4907671794879986</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>1</v>
+        <v>0.6178125143051147</v>
       </c>
       <c r="JB123" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>0.6813795381141482</v>
+        <v>0.4907672273145653</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.1953872442245483</v>
       </c>
       <c r="JB124" t="n">
-        <v>0.256106472331563</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC124" t="n">
-        <v>0.6813796337672816</v>
+        <v>0.4907673229676988</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.3729793727397919</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC125" t="n">
-        <v>0.6813795142008648</v>
+        <v>0.4907672034012819</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0</v>
+        <v>0.4996102452278137</v>
       </c>
       <c r="JB126" t="n">
-        <v>-0.6505587654005177</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC126" t="n">
-        <v>0.6813795221719593</v>
+        <v>0.4907672113723764</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-mamba2_repeat_3_000001.xlsx
+++ b/out/MLP-mamba2_repeat_3_000001.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.2870924472808838</v>
+        <v>0.2870922386646271</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.4399999999999999</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.7095795869827271</v>
+        <v>0.7095798254013062</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.58</v>
@@ -4121,7 +4121,7 @@
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0.3475010097026825</v>
+        <v>0.3475009500980377</v>
       </c>
       <c r="JB4" t="n">
         <v>-0.7199999999999999</v>
@@ -4916,7 +4916,7 @@
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>0.1942663043737411</v>
+        <v>0.1942644119262695</v>
       </c>
       <c r="JB5" t="n">
         <v>-0.7199999999999999</v>
@@ -5711,7 +5711,7 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0.2582058310508728</v>
+        <v>0.2582057416439056</v>
       </c>
       <c r="JB6" t="n">
         <v>-0.9999999999999998</v>
@@ -6506,7 +6506,7 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>0.2544656693935394</v>
+        <v>0.2544659078121185</v>
       </c>
       <c r="JB7" t="n">
         <v>-0.9999999999999998</v>
@@ -7301,7 +7301,7 @@
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0.3303287625312805</v>
+        <v>0.3303283751010895</v>
       </c>
       <c r="JB8" t="n">
         <v>-0.7199999999999999</v>
@@ -8096,7 +8096,7 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0.3631916344165802</v>
+        <v>0.3631912469863892</v>
       </c>
       <c r="JB9" t="n">
         <v>-0.7199999999999999</v>
@@ -8891,7 +8891,7 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0.5085197687149048</v>
+        <v>0.5085195899009705</v>
       </c>
       <c r="JB10" t="n">
         <v>-0.7199999999999999</v>
@@ -9686,7 +9686,7 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0.3054375052452087</v>
+        <v>0.3054340481758118</v>
       </c>
       <c r="JB11" t="n">
         <v>-0.1199999999999999</v>
@@ -10481,7 +10481,7 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0.2525750398635864</v>
+        <v>0.2525748014450073</v>
       </c>
       <c r="JB12" t="n">
         <v>0.16</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.3143773972988129</v>
+        <v>0.3143770098686218</v>
       </c>
       <c r="JB13" t="n">
         <v>0.16</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.5351336598396301</v>
+        <v>0.5351336002349854</v>
       </c>
       <c r="JB14" t="n">
         <v>0.4399999999999999</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.576799750328064</v>
+        <v>0.5768002271652222</v>
       </c>
       <c r="JB15" t="n">
         <v>0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.7204849720001221</v>
+        <v>0.7204857468605042</v>
       </c>
       <c r="JB16" t="n">
         <v>0.9999999999999998</v>
@@ -14456,7 +14456,7 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0.5754132270812988</v>
+        <v>0.5754143595695496</v>
       </c>
       <c r="JB17" t="n">
         <v>0.8599999999999999</v>
@@ -15251,7 +15251,7 @@
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0.4252062439918518</v>
+        <v>0.4252066612243652</v>
       </c>
       <c r="JB18" t="n">
         <v>0.7199999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.4794808626174927</v>
+        <v>0.479481428861618</v>
       </c>
       <c r="JB19" t="n">
         <v>0.4399999999999999</v>
@@ -16841,7 +16841,7 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>0.547101616859436</v>
+        <v>0.5471022129058838</v>
       </c>
       <c r="JB20" t="n">
         <v>-0.4399999999999999</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.3556079566478729</v>
+        <v>0.3556063771247864</v>
       </c>
       <c r="JB21" t="n">
         <v>-0.7199999999999999</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.2640213370323181</v>
+        <v>0.2640198469161987</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.8599999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.2505334615707397</v>
+        <v>0.2505324482917786</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.8599999999999999</v>
@@ -20021,7 +20021,7 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0.1727255582809448</v>
+        <v>0.1727258265018463</v>
       </c>
       <c r="JB24" t="n">
         <v>-0.8599999999999999</v>
@@ -20816,7 +20816,7 @@
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>0.51835697889328</v>
+        <v>0.518357515335083</v>
       </c>
       <c r="JB25" t="n">
         <v>-0.8599999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3558023869991302</v>
+        <v>0.3558025062084198</v>
       </c>
       <c r="JB26" t="n">
         <v>-0.8599999999999999</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.3072896599769592</v>
+        <v>0.3072896003723145</v>
       </c>
       <c r="JB28" t="n">
         <v>-0.7199999999999999</v>
@@ -23996,7 +23996,7 @@
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0.3962659239768982</v>
+        <v>0.3962655961513519</v>
       </c>
       <c r="JB29" t="n">
         <v>-0.1199999999999999</v>
@@ -24791,7 +24791,7 @@
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0.4285559952259064</v>
+        <v>0.4285559058189392</v>
       </c>
       <c r="JB30" t="n">
         <v>0.16</v>
@@ -25586,7 +25586,7 @@
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0.2365186512470245</v>
+        <v>0.2365192919969559</v>
       </c>
       <c r="JB31" t="n">
         <v>0.16</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.4184211790561676</v>
+        <v>0.4184210896492004</v>
       </c>
       <c r="JB32" t="n">
         <v>0.3</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.1322172731161118</v>
+        <v>0.1322173476219177</v>
       </c>
       <c r="JB33" t="n">
         <v>0.16</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4796909987926483</v>
+        <v>0.4796906709671021</v>
       </c>
       <c r="JB34" t="n">
         <v>0.4399999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.3126256465911865</v>
+        <v>0.3126252591609955</v>
       </c>
       <c r="JB35" t="n">
         <v>0.3</v>
@@ -29561,7 +29561,7 @@
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0.4269334971904755</v>
+        <v>0.426933079957962</v>
       </c>
       <c r="JB36" t="n">
         <v>0.5799999999999998</v>
@@ -30356,7 +30356,7 @@
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0.3863523006439209</v>
+        <v>0.3863521218299866</v>
       </c>
       <c r="JB37" t="n">
         <v>0.5799999999999998</v>
@@ -31151,7 +31151,7 @@
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0.5070080757141113</v>
+        <v>0.5070080161094666</v>
       </c>
       <c r="JB38" t="n">
         <v>0.8599999999999999</v>
@@ -31946,7 +31946,7 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0.6210157871246338</v>
+        <v>0.621015727519989</v>
       </c>
       <c r="JB39" t="n">
         <v>0.8599999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.8631818294525146</v>
+        <v>0.8631812930107117</v>
       </c>
       <c r="JB40" t="n">
         <v>0.9999999999999998</v>
@@ -33536,7 +33536,7 @@
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0.7516226768493652</v>
+        <v>0.7516211867332458</v>
       </c>
       <c r="JB41" t="n">
         <v>0.9999999999999998</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.9642179012298584</v>
+        <v>0.9642173647880554</v>
       </c>
       <c r="JB42" t="n">
         <v>0.9999999999999998</v>
@@ -35126,7 +35126,7 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>0.8121073246002197</v>
+        <v>0.8121051788330078</v>
       </c>
       <c r="JB43" t="n">
         <v>0.8599999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.9375625252723694</v>
+        <v>0.9375614523887634</v>
       </c>
       <c r="JB44" t="n">
         <v>0.5799999999999998</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.6953548789024353</v>
+        <v>0.6953514218330383</v>
       </c>
       <c r="JB45" t="n">
         <v>-0.3</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.01094582583755255</v>
+        <v>0.01094577461481094</v>
       </c>
       <c r="JB46" t="n">
         <v>-0.5799999999999998</v>
@@ -38306,7 +38306,7 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>0.2179289013147354</v>
+        <v>0.2179271578788757</v>
       </c>
       <c r="JB47" t="n">
         <v>-0.7199999999999999</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.01709781400859356</v>
+        <v>0.01709789410233498</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.8599999999999999</v>
@@ -39896,7 +39896,7 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0.494206041097641</v>
+        <v>0.4942024946212769</v>
       </c>
       <c r="JB49" t="n">
         <v>-0.5799999999999998</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.1966165900230408</v>
+        <v>0.1966167539358139</v>
       </c>
       <c r="JB50" t="n">
         <v>-0.5799999999999998</v>
@@ -41486,7 +41486,7 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>0.5493714809417725</v>
+        <v>0.5493713617324829</v>
       </c>
       <c r="JB51" t="n">
         <v>-0.3</v>
@@ -42281,7 +42281,7 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0.1937374174594879</v>
+        <v>0.1937376409769058</v>
       </c>
       <c r="JB52" t="n">
         <v>-0.4399999999999999</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.6452180743217468</v>
+        <v>0.6452142000198364</v>
       </c>
       <c r="JB53" t="n">
         <v>0.1600000000000001</v>
@@ -43871,7 +43871,7 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>0.2652173340320587</v>
+        <v>0.2652145326137543</v>
       </c>
       <c r="JB54" t="n">
         <v>-0.1199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.1778687536716461</v>
+        <v>0.1778690814971924</v>
       </c>
       <c r="JB55" t="n">
         <v>-0.7199999999999999</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.1975788176059723</v>
+        <v>0.1975791752338409</v>
       </c>
       <c r="JB57" t="n">
         <v>-0.9999999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.3115136027336121</v>
+        <v>0.3115137219429016</v>
       </c>
       <c r="JB58" t="n">
         <v>-0.9999999999999998</v>
@@ -47846,7 +47846,7 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>0.2721310257911682</v>
+        <v>0.272131085395813</v>
       </c>
       <c r="JB59" t="n">
         <v>-0.9999999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.2568386495113373</v>
+        <v>0.2568387687206268</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.7199999999999999</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.147075429558754</v>
+        <v>0.1470753997564316</v>
       </c>
       <c r="JB61" t="n">
         <v>0.16</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.4459397196769714</v>
+        <v>0.4459399580955505</v>
       </c>
       <c r="JB62" t="n">
         <v>0.1600000000000001</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.5478038191795349</v>
+        <v>0.5478038787841797</v>
       </c>
       <c r="JB63" t="n">
         <v>0.4399999999999999</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.3451752662658691</v>
+        <v>0.345175713300705</v>
       </c>
       <c r="JB64" t="n">
         <v>0.4399999999999999</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.2365031540393829</v>
+        <v>0.2365030497312546</v>
       </c>
       <c r="JB66" t="n">
         <v>0.16</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.8914751410484314</v>
+        <v>0.8914737105369568</v>
       </c>
       <c r="JB67" t="n">
         <v>0.1600000000000001</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.16587233543396</v>
+        <v>0.1658724099397659</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.7199999999999999</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.1619214713573456</v>
+        <v>0.1619215458631516</v>
       </c>
       <c r="JB69" t="n">
         <v>-0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.3377712368965149</v>
+        <v>0.3377710282802582</v>
       </c>
       <c r="JB70" t="n">
         <v>-0.7199999999999999</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.4509402215480804</v>
+        <v>0.4509409964084625</v>
       </c>
       <c r="JB71" t="n">
         <v>-0.7199999999999999</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.2788635492324829</v>
+        <v>0.2788636684417725</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.4399999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.2556007206439972</v>
+        <v>0.2556006610393524</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.4399999999999999</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.9558586478233337</v>
+        <v>0.9558578133583069</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.7199999999999999</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.1745253354310989</v>
+        <v>0.1745255142450333</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.7199999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.1508907824754715</v>
+        <v>0.150890976190567</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.224904477596283</v>
+        <v>0.2249051630496979</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.9999999999999998</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.09800317138433456</v>
+        <v>0.09800314158201218</v>
       </c>
       <c r="JB78" t="n">
         <v>-0.7199999999999999</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.2036522924900055</v>
+        <v>0.2036524713039398</v>
       </c>
       <c r="JB79" t="n">
         <v>-0.4399999999999999</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.4688417613506317</v>
+        <v>0.4688420295715332</v>
       </c>
       <c r="JB80" t="n">
         <v>0.1600000000000001</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.5553006529808044</v>
+        <v>0.5553008317947388</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.2687999606132507</v>
+        <v>0.2688004970550537</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.4707186818122864</v>
+        <v>0.4707192182540894</v>
       </c>
       <c r="JB83" t="n">
         <v>0.7199999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.3846917748451233</v>
+        <v>0.3846923112869263</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.5789629220962524</v>
+        <v>0.5789633393287659</v>
       </c>
       <c r="JB85" t="n">
         <v>0.4399999999999999</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.3535565733909607</v>
+        <v>0.353557288646698</v>
       </c>
       <c r="JB86" t="n">
         <v>0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.3039943277835846</v>
+        <v>0.3039949238300323</v>
       </c>
       <c r="JB87" t="n">
         <v>0.3</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.8388734459877014</v>
+        <v>0.8388733863830566</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.3</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3901277780532837</v>
+        <v>0.3901287317276001</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.7327395081520081</v>
+        <v>0.7327387928962708</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.2327285706996918</v>
+        <v>0.2327288240194321</v>
       </c>
       <c r="JB91" t="n">
         <v>-0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5457927584648132</v>
+        <v>0.5457938313484192</v>
       </c>
       <c r="JB92" t="n">
         <v>-0.4399999999999999</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.09769754856824875</v>
+        <v>0.0976976603269577</v>
       </c>
       <c r="JB93" t="n">
         <v>-0.7199999999999999</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3698757886886597</v>
+        <v>0.3698767423629761</v>
       </c>
       <c r="JB94" t="n">
         <v>-0.4399999999999999</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.3053628504276276</v>
+        <v>0.3053638339042664</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.7199999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.6117194294929504</v>
+        <v>0.6117201447486877</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.2792908847332001</v>
+        <v>0.2792916893959045</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.1600000000000001</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4177703559398651</v>
+        <v>0.4177712500095367</v>
       </c>
       <c r="JB98" t="n">
         <v>0.7199999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.7329034805297852</v>
+        <v>0.732903003692627</v>
       </c>
       <c r="JB99" t="n">
         <v>0.5799999999999998</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.6029258966445923</v>
+        <v>0.6029263138771057</v>
       </c>
       <c r="JB100" t="n">
         <v>0.5799999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.5134434700012207</v>
+        <v>0.5134434103965759</v>
       </c>
       <c r="JB101" t="n">
         <v>0.3</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.2455270439386368</v>
+        <v>0.2455273270606995</v>
       </c>
       <c r="JB102" t="n">
         <v>0.16</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.3067110776901245</v>
+        <v>0.3067110180854797</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.6113965511322021</v>
+        <v>0.6113970875740051</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.8599999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.1302557438611984</v>
+        <v>0.130255863070488</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.8599999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.1368108242750168</v>
+        <v>0.1368107795715332</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.8599999999999999</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.2335508614778519</v>
+        <v>0.233551487326622</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.8599999999999999</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.3958383500576019</v>
+        <v>0.3958387970924377</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.8599999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4419620335102081</v>
+        <v>0.4419626295566559</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.8599999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.3863091766834259</v>
+        <v>0.3863098919391632</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.8599999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.1953750997781754</v>
+        <v>0.1953756064176559</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.8599999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2087164670228958</v>
+        <v>0.2087169885635376</v>
       </c>
       <c r="JB112" t="n">
         <v>-0.1199999999999999</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.2294738590717316</v>
+        <v>0.2294740080833435</v>
       </c>
       <c r="JB113" t="n">
         <v>0.16</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.5906870365142822</v>
+        <v>0.5906876921653748</v>
       </c>
       <c r="JB115" t="n">
         <v>0.4399999999999999</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4911705851554871</v>
+        <v>0.491171270608902</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.1846119314432144</v>
+        <v>0.1846124231815338</v>
       </c>
       <c r="JB117" t="n">
         <v>0.16</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.3049150705337524</v>
+        <v>0.3049158751964569</v>
       </c>
       <c r="JB118" t="n">
         <v>-0.1199999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.2293042540550232</v>
+        <v>0.2293048948049545</v>
       </c>
       <c r="JB119" t="n">
         <v>-0.7199999999999999</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.1202573180198669</v>
+        <v>0.1202571839094162</v>
       </c>
       <c r="JB120" t="n">
         <v>-0.7199999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.785956859588623</v>
+        <v>0.7859567999839783</v>
       </c>
       <c r="JB121" t="n">
         <v>-0.4399999999999999</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.3485607504844666</v>
+        <v>0.3485612273216248</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.4399999999999999</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.6178125143051147</v>
+        <v>0.6178129911422729</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.1953872442245483</v>
+        <v>0.1953874230384827</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.5799999999999998</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.3729793727397919</v>
+        <v>0.3729799687862396</v>
       </c>
       <c r="JB125" t="n">
         <v>-0.5799999999999998</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.4996102452278137</v>
+        <v>0.4996103644371033</v>
       </c>
       <c r="JB126" t="n">
         <v>-0.5799999999999998</v>
